--- a/Boletim.xlsx
+++ b/Boletim.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\05308596379\Documents\Projetos\Dash_Ajuste\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\05308596379\Documents\Projetos\Dash_Boletim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707DDD0F-6668-4CF2-A2A2-8FCA6BBDF22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A96D987-1F4B-4747-BC74-388D740AA2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E375AB00-1BC7-4B12-8117-C5A7132EA4A3}"/>
+    <workbookView xWindow="-20760" yWindow="0" windowWidth="17280" windowHeight="8880" xr2:uid="{E375AB00-1BC7-4B12-8117-C5A7132EA4A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -86,10 +86,10 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>GAP</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Gap</t>
   </si>
 </sst>
 </file>
@@ -151,14 +151,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -499,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{023DDBAC-2800-4207-B41A-14E4349851DE}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -525,7 +523,7 @@
         <v>3039879.0571099971</v>
       </c>
       <c r="C2" s="4">
-        <v>5264114.8</v>
+        <v>5097858.92</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -536,7 +534,7 @@
         <v>2758459.9930600012</v>
       </c>
       <c r="C3" s="4">
-        <v>5264114.8</v>
+        <v>4846185.29</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -547,7 +545,7 @@
         <v>3546451.2607700052</v>
       </c>
       <c r="C4" s="4">
-        <v>5264114.8</v>
+        <v>4846185.29</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -558,7 +556,7 @@
         <v>5957084.3267000057</v>
       </c>
       <c r="C5" s="4">
-        <v>5264114.8</v>
+        <v>5220953.42</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -569,7 +567,7 @@
         <v>5070727.0836400008</v>
       </c>
       <c r="C6" s="4">
-        <v>5264114.8</v>
+        <v>5220953.42</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -580,7 +578,7 @@
         <v>3292389.7954199971</v>
       </c>
       <c r="C7" s="4">
-        <v>5264114.8</v>
+        <v>5220953.42</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -591,7 +589,7 @@
         <v>3330178.4400000027</v>
       </c>
       <c r="C8" s="4">
-        <v>5264114.8</v>
+        <v>5574124.6200000001</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -602,7 +600,7 @@
         <v>5771871.2899999954</v>
       </c>
       <c r="C9" s="4">
-        <v>5264114.8</v>
+        <v>5574124.6200000001</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -613,7 +611,7 @@
         <v>2075145.4000000001</v>
       </c>
       <c r="C10" s="4">
-        <v>5264114.8</v>
+        <v>5574124.6200000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -622,7 +620,7 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="4">
-        <v>5264114.8</v>
+        <v>5574124.6200000001</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -631,7 +629,7 @@
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="4">
-        <v>5264114.8</v>
+        <v>5574124.6200000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -640,12 +638,12 @@
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="4">
-        <v>5264114.8</v>
+        <v>5574124.6200000001</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>16</v>
+      <c r="A14" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="B14" s="4">
         <f>SUM(B2:B13)</f>
@@ -653,24 +651,18 @@
       </c>
       <c r="C14" s="4">
         <f>SUM(C2:C13)</f>
-        <v>63169377.599999987</v>
+        <v>63897837.479999989</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="5">
         <f>C14-B14</f>
-        <v>28327190.953299977</v>
-      </c>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C16" s="5"/>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C18" s="5"/>
+        <v>29055650.83329998</v>
+      </c>
+      <c r="C15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Boletim.xlsx
+++ b/Boletim.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\05308596379\Documents\Projetos\Dash_Boletim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A96D987-1F4B-4747-BC74-388D740AA2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92502CAD-0BFA-4F8E-9659-BF9ED42D5E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20760" yWindow="0" windowWidth="17280" windowHeight="8880" xr2:uid="{E375AB00-1BC7-4B12-8117-C5A7132EA4A3}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E375AB00-1BC7-4B12-8117-C5A7132EA4A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -618,7 +618,9 @@
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="3">
+        <v>6183721.4299999997</v>
+      </c>
       <c r="C11" s="4">
         <v>5574124.6200000001</v>
       </c>
@@ -647,7 +649,7 @@
       </c>
       <c r="B14" s="4">
         <f>SUM(B2:B13)</f>
-        <v>34842186.64670001</v>
+        <v>41025908.076700009</v>
       </c>
       <c r="C14" s="4">
         <f>SUM(C2:C13)</f>
@@ -660,7 +662,7 @@
       </c>
       <c r="B15" s="5">
         <f>C14-B14</f>
-        <v>29055650.83329998</v>
+        <v>22871929.40329998</v>
       </c>
       <c r="C15" s="6"/>
     </row>

--- a/Boletim.xlsx
+++ b/Boletim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\05308596379\Documents\Projetos\Dash_Boletim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92502CAD-0BFA-4F8E-9659-BF9ED42D5E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D265765-7B2B-4A09-8622-A21D4ADC4E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E375AB00-1BC7-4B12-8117-C5A7132EA4A3}"/>
   </bookViews>
@@ -96,7 +96,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
@@ -151,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -163,6 +164,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,14 +501,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{023DDBAC-2800-4207-B41A-14E4349851DE}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -515,7 +521,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -526,7 +532,7 @@
         <v>5097858.92</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -537,7 +543,7 @@
         <v>4846185.29</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -548,7 +554,7 @@
         <v>4846185.29</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -559,7 +565,7 @@
         <v>5220953.42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -570,7 +576,7 @@
         <v>5220953.42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -581,7 +587,7 @@
         <v>5220953.42</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -592,7 +598,7 @@
         <v>5574124.6200000001</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -603,29 +609,33 @@
         <v>5574124.6200000001</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
-        <v>2075145.4000000001</v>
+      <c r="B10" s="9">
+        <v>1928926.8</v>
       </c>
       <c r="C10" s="4">
         <v>5574124.6200000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="3">
-        <v>6183721.4299999997</v>
+      <c r="B11" s="9">
+        <v>6329940.0299999993</v>
       </c>
       <c r="C11" s="4">
         <v>5574124.6200000001</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -634,7 +644,7 @@
         <v>5574124.6200000001</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -642,8 +652,9 @@
       <c r="C13" s="4">
         <v>5574124.6200000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
@@ -656,7 +667,7 @@
         <v>63897837.479999989</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
